--- a/data/source/GSSPs.xlsx
+++ b/data/source/GSSPs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nick/work/ics/gssps/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A60E340-3388-1E46-BF5F-BBED6554D2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED93A50A-8E8B-1247-B497-66E22D3EF178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7800" yWindow="2620" windowWidth="43300" windowHeight="27100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="720" windowWidth="43300" windowHeight="27100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GSSPs" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="794">
   <si>
     <t>Type</t>
   </si>
@@ -876,9 +876,6 @@
     <t>Anticipated 2009</t>
   </si>
   <si>
-    <t>Albertiana 36, 2007.</t>
-  </si>
-  <si>
     <t>https://data.stratigraphy.org/data/gssps/Olenekian</t>
   </si>
   <si>
@@ -892,9 +889,6 @@
   </si>
   <si>
     <t>Conodont FAD Neospathodus waageni, just above base of Rohillites rohilla ammonite zone, and below lowest occurrence of Flemingites and Euflemingites ammonite genera. Within a prominent positive Carbon-13 peak, and just above widely recognizable sequence boundary.</t>
-  </si>
-  <si>
-    <t>Albertiana 36, 2007</t>
   </si>
   <si>
     <t>https://data.stratigraphy.org/data/gssps/Induan</t>
@@ -4422,17 +4416,9 @@
     <t>https://doi.org/10.18814/epiiugs/2009/v32i4/001</t>
   </si>
   <si>
-    <t>https://doi.org/10.18814/epiiugs/2018/018016
-https://stratigraphy.org/gssps/files/meghalayan.pdf</t>
-  </si>
-  <si>
     <t>https://doi.org/10.18814/epiiugs/2008/v31i2/016
 https://doi.org/10.18814/epiiugs/2018/018016
 https://stratigraphy.org/gssps/files/meghalayan.pdf</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.18814/epiiugs/2020/020080
-https://stratigraphy.org/gssps/files/chibanian.pdf</t>
   </si>
   <si>
     <t>https://doi.org/10.18814/epiiugs/1985/v8i2/009
@@ -4650,6 +4636,51 @@
     <t>El Pintado 1 GSSP: Loydell et al., Episodes forthcoming
 https://doi.org/10.18814/epiiugs/1985/v8i2/005
 Cefn-Cerig Rd GSSP: Geol. Series, Nat. Mus. Wales 1989; 9: 36-50</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Krystyn, L., Richoz, S., &amp; Bhargava, O. N. (2007). The Induan-Olenekian Boundary (IOB) in Mud–an update of the candidate GSSP section M04. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Albertiana</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 33-45.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.18814/epiiugs/2018/018016</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.18814/epiiugs/2020/020080</t>
   </si>
 </sst>
 </file>
@@ -5007,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
@@ -5028,7 +5059,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>8</v>
@@ -5042,16 +5073,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>12</v>
@@ -5062,8 +5093,8 @@
       <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>728</v>
+      <c r="K2" s="6" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -5074,10 +5105,10 @@
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
@@ -5094,8 +5125,8 @@
       <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>728</v>
+      <c r="K3" s="6" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -5106,10 +5137,10 @@
         <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
@@ -5127,7 +5158,7 @@
         <v>24</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5138,10 +5169,10 @@
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>26</v>
@@ -5168,10 +5199,10 @@
         <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>32</v>
@@ -5191,22 +5222,22 @@
       <c r="J6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>730</v>
+      <c r="K6" s="6" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>32</v>
@@ -5235,10 +5266,10 @@
         <v>43</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E8" t="s">
         <v>44</v>
@@ -5259,7 +5290,7 @@
         <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -5270,10 +5301,10 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>51</v>
@@ -5294,7 +5325,7 @@
         <v>56</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5305,10 +5336,10 @@
         <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>58</v>
@@ -5329,7 +5360,7 @@
         <v>63</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5340,10 +5371,10 @@
         <v>64</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>65</v>
@@ -5364,7 +5395,7 @@
         <v>70</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -5375,10 +5406,10 @@
         <v>71</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>72</v>
@@ -5393,13 +5424,13 @@
         <v>75</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>70</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5410,10 +5441,10 @@
         <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>77</v>
@@ -5428,13 +5459,13 @@
         <v>80</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>81</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -5445,10 +5476,10 @@
         <v>82</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>83</v>
@@ -5463,13 +5494,13 @@
         <v>86</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>87</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5480,10 +5511,10 @@
         <v>88</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>89</v>
@@ -5512,17 +5543,17 @@
         <v>94</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>95</v>
       </c>
       <c r="G16" s="7"/>
       <c r="I16" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -5535,10 +5566,10 @@
         <v>96</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>97</v>
@@ -5553,13 +5584,13 @@
         <v>100</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>101</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5570,10 +5601,10 @@
         <v>102</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>103</v>
@@ -5585,7 +5616,7 @@
         <v>105</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>106</v>
@@ -5605,10 +5636,10 @@
         <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>110</v>
@@ -5623,13 +5654,13 @@
         <v>113</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>114</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -5640,10 +5671,10 @@
         <v>115</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>116</v>
@@ -5658,7 +5689,7 @@
         <v>119</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>37</v>
@@ -5675,17 +5706,17 @@
         <v>121</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G21" s="7"/>
       <c r="I21" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -5698,10 +5729,10 @@
         <v>123</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>124</v>
@@ -5722,7 +5753,7 @@
         <v>129</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5733,10 +5764,10 @@
         <v>130</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>131</v>
@@ -5757,7 +5788,7 @@
         <v>81</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5768,10 +5799,10 @@
         <v>136</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>137</v>
@@ -5792,7 +5823,7 @@
         <v>142</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5803,10 +5834,10 @@
         <v>143</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>144</v>
@@ -5827,7 +5858,7 @@
         <v>142</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5838,10 +5869,10 @@
         <v>147</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>148</v>
@@ -5862,7 +5893,7 @@
         <v>153</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -5873,10 +5904,10 @@
         <v>154</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>155</v>
@@ -5891,13 +5922,13 @@
         <v>158</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>159</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -5908,10 +5939,10 @@
         <v>160</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>161</v>
@@ -5943,10 +5974,10 @@
         <v>168</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>169</v>
@@ -5961,13 +5992,13 @@
         <v>172</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>173</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5978,10 +6009,10 @@
         <v>174</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>175</v>
@@ -5996,7 +6027,7 @@
         <v>178</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>179</v>
@@ -6013,10 +6044,10 @@
         <v>181</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>182</v>
@@ -6031,13 +6062,13 @@
         <v>185</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>81</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6048,10 +6079,10 @@
         <v>186</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>187</v>
@@ -6066,13 +6097,13 @@
         <v>190</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>191</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -6083,10 +6114,10 @@
         <v>192</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>193</v>
@@ -6098,7 +6129,7 @@
         <v>195</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>107</v>
@@ -6115,17 +6146,17 @@
         <v>197</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>198</v>
       </c>
       <c r="G34" s="7"/>
       <c r="I34" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -6138,10 +6169,10 @@
         <v>199</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>200</v>
@@ -6153,7 +6184,7 @@
         <v>202</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>41</v>
@@ -6170,10 +6201,10 @@
         <v>204</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>205</v>
@@ -6185,7 +6216,7 @@
         <v>207</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>208</v>
@@ -6202,17 +6233,17 @@
         <v>210</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>211</v>
       </c>
       <c r="G37" s="7"/>
       <c r="I37" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
@@ -6225,14 +6256,14 @@
         <v>212</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G38" s="7"/>
       <c r="I38" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
@@ -6245,17 +6276,17 @@
         <v>213</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>214</v>
       </c>
       <c r="G39" s="7"/>
       <c r="I39" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
@@ -6268,10 +6299,10 @@
         <v>215</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>216</v>
@@ -6280,7 +6311,7 @@
         <v>217</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>179</v>
@@ -6297,17 +6328,17 @@
         <v>219</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G41" s="7"/>
       <c r="I41" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
@@ -6320,17 +6351,17 @@
         <v>221</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>222</v>
       </c>
       <c r="G42" s="7"/>
       <c r="I42" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
@@ -6343,10 +6374,10 @@
         <v>223</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>224</v>
@@ -6361,13 +6392,13 @@
         <v>227</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>142</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -6378,10 +6409,10 @@
         <v>228</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>229</v>
@@ -6396,13 +6427,13 @@
         <v>232</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>101</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6413,10 +6444,10 @@
         <v>233</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>234</v>
@@ -6431,13 +6462,13 @@
         <v>237</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>70</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -6448,10 +6479,10 @@
         <v>238</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>239</v>
@@ -6466,13 +6497,13 @@
         <v>242</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>243</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6483,10 +6514,10 @@
         <v>244</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>245</v>
@@ -6501,13 +6532,13 @@
         <v>248</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>249</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6518,10 +6549,10 @@
         <v>250</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>251</v>
@@ -6536,13 +6567,13 @@
         <v>254</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>70</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -6553,10 +6584,10 @@
         <v>255</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>256</v>
@@ -6571,13 +6602,13 @@
         <v>259</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>260</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -6588,17 +6619,17 @@
         <v>261</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>262</v>
       </c>
       <c r="G50" s="7"/>
       <c r="I50" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
@@ -6611,17 +6642,17 @@
         <v>263</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>264</v>
       </c>
       <c r="G51" s="7"/>
       <c r="I51" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
@@ -6634,10 +6665,10 @@
         <v>265</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>266</v>
@@ -6652,13 +6683,13 @@
         <v>269</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J52" s="7" t="s">
         <v>142</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -6669,10 +6700,10 @@
         <v>270</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>271</v>
@@ -6687,13 +6718,13 @@
         <v>274</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="J53" s="7" t="s">
         <v>249</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6704,10 +6735,10 @@
         <v>275</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>276</v>
@@ -6716,7 +6747,7 @@
         <v>277</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>278</v>
@@ -6724,8 +6755,8 @@
       <c r="J54" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>280</v>
+      <c r="K54" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6733,31 +6764,31 @@
         <v>9</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="F55" s="1" t="s">
+      <c r="G55" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="H55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="J55" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>286</v>
+      <c r="K55" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6765,34 +6796,34 @@
         <v>9</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="G56" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="I56" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="J56" s="7" t="s">
         <v>159</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6800,34 +6831,34 @@
         <v>9</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G57" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G57" s="7" t="s">
+      <c r="I57" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="J57" s="7" t="s">
         <v>249</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -6835,34 +6866,34 @@
         <v>9</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="G58" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="G58" s="7" t="s">
+      <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="J58" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>304</v>
-      </c>
       <c r="K58" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -6870,34 +6901,34 @@
         <v>9</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="G59" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="G59" s="7" t="s">
+      <c r="I59" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="J59" s="7" t="s">
         <v>159</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -6905,34 +6936,34 @@
         <v>9</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="G60" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="G60" s="7" t="s">
+      <c r="I60" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="J60" s="7" t="s">
         <v>159</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -6940,34 +6971,34 @@
         <v>9</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="G61" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="G61" s="7" t="s">
+      <c r="I61" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="J61" s="7" t="s">
         <v>159</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6975,20 +7006,20 @@
         <v>9</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G62" s="7"/>
       <c r="J62" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K62" s="7"/>
     </row>
@@ -6997,34 +7028,34 @@
         <v>9</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="G63" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="H63" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="I63" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="J63" s="7" t="s">
         <v>166</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -7032,34 +7063,34 @@
         <v>9</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="G64" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="I64" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="J64" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7067,34 +7098,34 @@
         <v>9</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="G65" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="I65" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="J65" s="7" t="s">
         <v>101</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -7102,20 +7133,20 @@
         <v>9</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G66" s="7"/>
       <c r="I66" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
@@ -7125,20 +7156,20 @@
         <v>9</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G67" s="7"/>
       <c r="I67" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
@@ -7148,20 +7179,20 @@
         <v>9</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G68" s="7"/>
       <c r="I68" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -7171,31 +7202,31 @@
         <v>9</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G69" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F69" s="1" t="s">
+      <c r="H69" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="I69" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="J69" s="7" t="s">
         <v>101</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7203,20 +7234,20 @@
         <v>9</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G70" s="7"/>
       <c r="I70" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
@@ -7226,31 +7257,31 @@
         <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G71" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="H71" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="I71" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J71" s="7" t="s">
         <v>142</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -7258,31 +7289,31 @@
         <v>9</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G72" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="G72" s="7" t="s">
+      <c r="I72" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="J72" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>369</v>
-      </c>
       <c r="K72" s="6" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -7290,31 +7321,31 @@
         <v>9</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G73" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="H73" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G73" s="7" t="s">
+      <c r="I73" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="J73" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="J73" s="7" t="s">
-        <v>375</v>
-      </c>
       <c r="K73" s="6" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7322,31 +7353,31 @@
         <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G74" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="G74" s="7" t="s">
+      <c r="I74" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="J74" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="J74" s="7" t="s">
-        <v>381</v>
-      </c>
       <c r="K74" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -7354,31 +7385,31 @@
         <v>9</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G75" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="G75" s="7" t="s">
+      <c r="I75" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="J75" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>387</v>
-      </c>
       <c r="K75" s="6" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7386,31 +7417,31 @@
         <v>9</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G76" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="I76" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="J76" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="J76" s="7" t="s">
-        <v>393</v>
-      </c>
       <c r="K76" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7418,31 +7449,31 @@
         <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="G77" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="I77" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="J77" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="J77" s="7" t="s">
-        <v>399</v>
-      </c>
       <c r="K77" s="6" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -7450,31 +7481,31 @@
         <v>9</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G78" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="I78" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="J78" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="J78" s="7" t="s">
-        <v>405</v>
-      </c>
       <c r="K78" s="6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="153" customHeight="1" x14ac:dyDescent="0.2">
@@ -7482,31 +7513,31 @@
         <v>9</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G79" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="H79" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="I79" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="J79" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>410</v>
-      </c>
       <c r="K79" s="6" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -7514,31 +7545,31 @@
         <v>9</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G80" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="G80" s="7" t="s">
+      <c r="I80" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="J80" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J80" s="7" t="s">
-        <v>415</v>
-      </c>
       <c r="K80" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="53" customHeight="1" x14ac:dyDescent="0.2">
@@ -7546,31 +7577,31 @@
         <v>9</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G81" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="H81" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G81" s="7" t="s">
+      <c r="I81" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="J81" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J81" s="7" t="s">
-        <v>420</v>
-      </c>
       <c r="K81" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="53" customHeight="1" x14ac:dyDescent="0.2">
@@ -7578,31 +7609,31 @@
         <v>9</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G82" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="J82" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>420</v>
-      </c>
       <c r="K82" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="53" customHeight="1" x14ac:dyDescent="0.2">
@@ -7610,31 +7641,31 @@
         <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="G83" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="H83" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="G83" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="I83" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="204" customHeight="1" x14ac:dyDescent="0.2">
@@ -7642,34 +7673,34 @@
         <v>9</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G84" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="F84" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G84" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="I84" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -7677,31 +7708,31 @@
         <v>9</v>
       </c>
       <c r="B85" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G85" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F85" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="G85" s="7" t="s">
+      <c r="I85" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="K85" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -7709,31 +7740,31 @@
         <v>9</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G86" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F86" s="1" t="s">
+      <c r="H86" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="G86" s="7" t="s">
+      <c r="I86" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="K86" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -7741,31 +7772,31 @@
         <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G87" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="H87" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="I87" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7773,31 +7804,31 @@
         <v>9</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="G88" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="H88" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="G88" s="7" t="s">
+      <c r="I88" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="J88" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>449</v>
-      </c>
       <c r="K88" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7805,31 +7836,31 @@
         <v>9</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G89" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F89" s="1" t="s">
+      <c r="H89" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="G89" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="I89" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7837,31 +7868,31 @@
         <v>9</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G90" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="G90" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="I90" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J90" s="7" t="s">
         <v>191</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7869,31 +7900,31 @@
         <v>9</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G91" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F91" s="1" t="s">
+      <c r="H91" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="G91" s="7" t="s">
+      <c r="I91" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="J91" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>462</v>
-      </c>
       <c r="K91" s="6" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -7901,31 +7932,31 @@
         <v>9</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G92" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="H92" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="I92" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J92" s="7" t="s">
         <v>87</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7933,31 +7964,31 @@
         <v>9</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G93" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F93" s="1" t="s">
+      <c r="H93" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="G93" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="I93" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J93" s="7" t="s">
         <v>191</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7965,31 +7996,31 @@
         <v>9</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G94" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F94" s="1" t="s">
+      <c r="H94" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="G94" s="7" t="s">
+      <c r="I94" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="J94" s="7" t="s">
         <v>70</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -7997,20 +8028,20 @@
         <v>9</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G95" s="7"/>
       <c r="I95" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
@@ -8020,31 +8051,31 @@
         <v>9</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="G96" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="H96" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G96" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="I96" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J96" s="7" t="s">
         <v>129</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -8052,31 +8083,31 @@
         <v>9</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="G97" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="H97" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="G97" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="I97" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J97" s="7" t="s">
         <v>81</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -8084,31 +8115,31 @@
         <v>9</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F98" s="1" t="s">
+      <c r="H98" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="G98" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="I98" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="J98" s="7" t="s">
         <v>142</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -8116,31 +8147,31 @@
         <v>9</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G99" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F99" s="1" t="s">
+      <c r="H99" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="G99" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="I99" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -8148,20 +8179,20 @@
         <v>9</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G100" s="7"/>
       <c r="I100" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
@@ -8171,17 +8202,17 @@
         <v>9</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G101" s="7"/>
       <c r="I101" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
@@ -8191,17 +8222,17 @@
         <v>9</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G102" s="7"/>
       <c r="I102" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
@@ -8211,17 +8242,17 @@
         <v>9</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G103" s="7"/>
       <c r="I103" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
@@ -8231,31 +8262,31 @@
         <v>9</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G104" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="H104" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G104" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="I104" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="J104" s="7" t="s">
         <v>114</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -8263,31 +8294,31 @@
         <v>9</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G105" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F105" s="1" t="s">
+      <c r="H105" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G105" s="7" t="s">
+      <c r="I105" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="J105" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="K105" s="6" t="s">
         <v>509</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -8295,347 +8326,347 @@
         <v>9</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="6" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G110" s="7"/>
       <c r="J110" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G116" s="7"/>
       <c r="J116" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H118" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="G118" s="7" t="s">
+      <c r="I118" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>532</v>
       </c>
       <c r="J118" s="7" t="s">
         <v>41</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="J119" s="7" t="s">
         <v>166</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -8707,6 +8738,9 @@
     <hyperlink ref="C16" r:id="rId65" xr:uid="{A51B06DB-D352-9945-B4A0-D219C201B969}"/>
     <hyperlink ref="B85" r:id="rId66" xr:uid="{B9C231D0-8309-6541-A809-5C9FF68FD3CC}"/>
     <hyperlink ref="E5" r:id="rId67" xr:uid="{4AB952BE-4C9C-464A-9DFD-97E157A36AC1}"/>
+    <hyperlink ref="K2" r:id="rId68" xr:uid="{10410044-93E1-3943-A238-6D394896850F}"/>
+    <hyperlink ref="K3" r:id="rId69" xr:uid="{F3BF6BCC-D35C-F349-8473-69A6FF7568B8}"/>
+    <hyperlink ref="K6" r:id="rId70" xr:uid="{80089330-3C16-7F43-A2D7-84ED4FB9866F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8726,15 +8760,15 @@
         <v>233</v>
       </c>
       <c r="B1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -8742,7 +8776,7 @@
         <v>192</v>
       </c>
       <c r="B3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -8750,7 +8784,7 @@
         <v>275</v>
       </c>
       <c r="B4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8758,7 +8792,7 @@
         <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -8766,23 +8800,23 @@
         <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B8" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8790,7 +8824,7 @@
         <v>228</v>
       </c>
       <c r="B9" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -8798,7 +8832,7 @@
         <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -8806,15 +8840,15 @@
         <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B12" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -8822,7 +8856,7 @@
         <v>223</v>
       </c>
       <c r="B13" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -8830,7 +8864,7 @@
         <v>212</v>
       </c>
       <c r="B14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8838,7 +8872,7 @@
         <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -8846,7 +8880,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -8854,39 +8888,39 @@
         <v>221</v>
       </c>
       <c r="B17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B19" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B20" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B21" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -8894,15 +8928,15 @@
         <v>160</v>
       </c>
       <c r="B22" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B23" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -8910,7 +8944,7 @@
         <v>265</v>
       </c>
       <c r="B24" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -8918,15 +8952,15 @@
         <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -8934,7 +8968,7 @@
         <v>102</v>
       </c>
       <c r="B27" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -8942,7 +8976,7 @@
         <v>174</v>
       </c>
       <c r="B28" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -8950,79 +8984,79 @@
         <v>147</v>
       </c>
       <c r="B29" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B31" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B32" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B33" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B34" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B36" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B37" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -9030,23 +9064,23 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B41" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -9054,23 +9088,23 @@
         <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B43" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -9078,7 +9112,7 @@
         <v>204</v>
       </c>
       <c r="B45" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -9086,55 +9120,55 @@
         <v>255</v>
       </c>
       <c r="B46" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B49" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
@@ -9142,15 +9176,15 @@
         <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B54" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
@@ -9158,7 +9192,7 @@
         <v>270</v>
       </c>
       <c r="B55" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
@@ -9166,23 +9200,23 @@
         <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -9190,7 +9224,7 @@
         <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
@@ -9198,7 +9232,7 @@
         <v>154</v>
       </c>
       <c r="B60" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -9206,7 +9240,7 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -9214,23 +9248,23 @@
         <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B63" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
@@ -9238,7 +9272,7 @@
         <v>263</v>
       </c>
       <c r="B65" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
@@ -9246,15 +9280,15 @@
         <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B67" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -9262,15 +9296,15 @@
         <v>219</v>
       </c>
       <c r="B68" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -9278,7 +9312,7 @@
         <v>57</v>
       </c>
       <c r="B70" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -9286,15 +9320,15 @@
         <v>244</v>
       </c>
       <c r="B71" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B72" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -9302,7 +9336,7 @@
         <v>115</v>
       </c>
       <c r="B73" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -9310,23 +9344,23 @@
         <v>261</v>
       </c>
       <c r="B74" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B76" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
@@ -9334,23 +9368,23 @@
         <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B78" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B79" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
@@ -9358,7 +9392,7 @@
         <v>168</v>
       </c>
       <c r="B80" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -9366,15 +9400,15 @@
         <v>143</v>
       </c>
       <c r="B81" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B82" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -9382,15 +9416,15 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B84" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -9398,15 +9432,15 @@
         <v>250</v>
       </c>
       <c r="B85" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B86" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
@@ -9414,7 +9448,7 @@
         <v>136</v>
       </c>
       <c r="B87" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
@@ -9422,7 +9456,7 @@
         <v>213</v>
       </c>
       <c r="B88" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -9430,7 +9464,7 @@
         <v>238</v>
       </c>
       <c r="B89" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
@@ -9438,23 +9472,23 @@
         <v>76</v>
       </c>
       <c r="B90" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B91" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B92" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -9462,7 +9496,7 @@
         <v>181</v>
       </c>
       <c r="B93" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
@@ -9470,7 +9504,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
@@ -9478,39 +9512,39 @@
         <v>210</v>
       </c>
       <c r="B95" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B96" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B97" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B98" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B99" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
@@ -9518,7 +9552,7 @@
         <v>130</v>
       </c>
       <c r="B100" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -9526,7 +9560,7 @@
         <v>64</v>
       </c>
       <c r="B101" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/GSSPs.xlsx
+++ b/data/source/GSSPs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nick/work/ics/gssps/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED93A50A-8E8B-1247-B497-66E22D3EF178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C43F8D-ABE3-6D47-81EB-528960C07475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="720" windowWidth="43300" windowHeight="27100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="720" windowWidth="43300" windowHeight="27100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GSSPs" sheetId="1" r:id="rId1"/>
@@ -4416,11 +4416,6 @@
     <t>https://doi.org/10.18814/epiiugs/2009/v32i4/001</t>
   </si>
   <si>
-    <t>https://doi.org/10.18814/epiiugs/2008/v31i2/016
-https://doi.org/10.18814/epiiugs/2018/018016
-https://stratigraphy.org/gssps/files/meghalayan.pdf</t>
-  </si>
-  <si>
     <t>https://doi.org/10.18814/epiiugs/1985/v8i2/009
 https://doi.org/10.18814/epiiugs/2012/v35i3/001
 https://doi.org/10.1016/j.quaint.2019.05.018</t>
@@ -4681,6 +4676,10 @@
   </si>
   <si>
     <t>https://doi.org/10.18814/epiiugs/2020/020080</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.18814/epiiugs/2008/v31i2/016
+https://doi.org/10.18814/epiiugs/2018/018016</t>
   </si>
 </sst>
 </file>
@@ -5094,7 +5093,7 @@
         <v>14</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -5126,7 +5125,7 @@
         <v>14</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -5158,7 +5157,7 @@
         <v>24</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>726</v>
+        <v>793</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5223,7 +5222,7 @@
         <v>37</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -5290,7 +5289,7 @@
         <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -5325,7 +5324,7 @@
         <v>56</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5360,7 +5359,7 @@
         <v>63</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5395,7 +5394,7 @@
         <v>70</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -5430,7 +5429,7 @@
         <v>70</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5465,7 +5464,7 @@
         <v>81</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -5500,7 +5499,7 @@
         <v>87</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5590,7 +5589,7 @@
         <v>101</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5660,7 +5659,7 @@
         <v>114</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -5753,7 +5752,7 @@
         <v>129</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5788,7 +5787,7 @@
         <v>81</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -5823,7 +5822,7 @@
         <v>142</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5858,7 +5857,7 @@
         <v>142</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -5893,7 +5892,7 @@
         <v>153</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -5928,7 +5927,7 @@
         <v>159</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -5998,7 +5997,7 @@
         <v>173</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6068,7 +6067,7 @@
         <v>81</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6103,7 +6102,7 @@
         <v>191</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -6433,7 +6432,7 @@
         <v>101</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6468,7 +6467,7 @@
         <v>70</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -6503,7 +6502,7 @@
         <v>243</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6538,7 +6537,7 @@
         <v>249</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6573,7 +6572,7 @@
         <v>70</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -6608,7 +6607,7 @@
         <v>260</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -6689,7 +6688,7 @@
         <v>142</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -6724,7 +6723,7 @@
         <v>249</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6756,7 +6755,7 @@
         <v>279</v>
       </c>
       <c r="K54" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6788,7 +6787,7 @@
         <v>279</v>
       </c>
       <c r="K55" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6823,7 +6822,7 @@
         <v>159</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -6858,7 +6857,7 @@
         <v>249</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -6893,7 +6892,7 @@
         <v>302</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -6928,7 +6927,7 @@
         <v>159</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -6963,7 +6962,7 @@
         <v>159</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -6998,7 +6997,7 @@
         <v>159</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -7125,7 +7124,7 @@
         <v>101</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -7226,7 +7225,7 @@
         <v>101</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7281,7 +7280,7 @@
         <v>142</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -7313,7 +7312,7 @@
         <v>367</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -7345,7 +7344,7 @@
         <v>373</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7377,7 +7376,7 @@
         <v>379</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -7409,7 +7408,7 @@
         <v>385</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7441,7 +7440,7 @@
         <v>391</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7473,7 +7472,7 @@
         <v>397</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -7505,7 +7504,7 @@
         <v>403</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="153" customHeight="1" x14ac:dyDescent="0.2">
@@ -7537,7 +7536,7 @@
         <v>408</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -7569,7 +7568,7 @@
         <v>413</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="53" customHeight="1" x14ac:dyDescent="0.2">
@@ -7601,7 +7600,7 @@
         <v>418</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="53" customHeight="1" x14ac:dyDescent="0.2">
@@ -7633,7 +7632,7 @@
         <v>418</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="53" customHeight="1" x14ac:dyDescent="0.2">
@@ -7665,7 +7664,7 @@
         <v>418</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="204" customHeight="1" x14ac:dyDescent="0.2">
@@ -7682,7 +7681,7 @@
         <v>605</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>426</v>
@@ -7700,7 +7699,7 @@
         <v>418</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -7732,7 +7731,7 @@
         <v>433</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -7764,7 +7763,7 @@
         <v>438</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -7796,7 +7795,7 @@
         <v>413</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7828,7 +7827,7 @@
         <v>447</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7860,7 +7859,7 @@
         <v>447</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7892,7 +7891,7 @@
         <v>191</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7924,7 +7923,7 @@
         <v>460</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -7956,7 +7955,7 @@
         <v>87</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -7988,7 +7987,7 @@
         <v>191</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -8020,7 +8019,7 @@
         <v>70</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -8075,7 +8074,7 @@
         <v>129</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -8139,7 +8138,7 @@
         <v>142</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -8171,7 +8170,7 @@
         <v>447</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -8286,7 +8285,7 @@
         <v>114</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -8340,7 +8339,7 @@
       <c r="G106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8364,7 +8363,7 @@
         <v>367</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8388,7 +8387,7 @@
         <v>367</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8412,7 +8411,7 @@
         <v>367</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8436,7 +8435,7 @@
         <v>367</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8460,7 +8459,7 @@
         <v>367</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8484,7 +8483,7 @@
         <v>367</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8508,7 +8507,7 @@
         <v>367</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8532,7 +8531,7 @@
         <v>367</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8556,7 +8555,7 @@
         <v>524</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8580,7 +8579,7 @@
         <v>524</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -8604,7 +8603,7 @@
         <v>524</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -8636,7 +8635,7 @@
         <v>41</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="119" customHeight="1" x14ac:dyDescent="0.2">
